--- a/CSV/Swamp Hut.xlsx
+++ b/CSV/Swamp Hut.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willem/Documents/GitHub/friend-zone/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willem/Documents/GitHub/friend-zone/CSV/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11EAFBD5-E30F-0443-820F-01C3A6A99F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD279805-3B26-0A4A-918D-A0BDAC0B71ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19460" yWindow="780" windowWidth="10000" windowHeight="19100" xr2:uid="{EF5563DD-86E3-44AF-B99F-9E11ACF57133}"/>
+    <workbookView xWindow="280" yWindow="9880" windowWidth="10000" windowHeight="7900" xr2:uid="{EF5563DD-86E3-44AF-B99F-9E11ACF57133}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,13 +41,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>nummer</t>
-  </si>
-  <si>
     <t>X</t>
   </si>
   <si>
     <t>Z</t>
+  </si>
+  <si>
+    <t>Swamp Hut</t>
   </si>
 </sst>
 </file>
@@ -429,23 +429,29 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
+      </c>
+      <c r="B2">
+        <v>-5000</v>
+      </c>
+      <c r="C2">
+        <v>2856</v>
       </c>
     </row>
   </sheetData>
